--- a/Data/EXCEL/Transfer/salemon/202208/1592-salemon-202208.xlsx
+++ b/Data/EXCEL/Transfer/salemon/202208/1592-salemon-202208.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\WORKSPACES\GoodinfoWebData\salemon\202208\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\WORKSPACES\xls2xlsx\Transfer\202208\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8FD0D3CB-3F04-4B42-87DF-425BB5DAC6B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{2D4EB353-CC9D-479E-ADF2-EA6E2472BB82}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3510" yWindow="1395" windowWidth="22035" windowHeight="12855"/>
+    <workbookView xWindow="390" yWindow="390" windowWidth="30645" windowHeight="19905"/>
   </bookViews>
   <sheets>
     <sheet name="1592-salemon-202208" sheetId="2" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="570" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="342" uniqueCount="18">
   <si>
     <t>月別</t>
   </si>
@@ -80,7 +80,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="25" x14ac:knownFonts="1">
+  <fonts count="26" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -246,7 +246,7 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="新細明體"/>
-      <family val="2"/>
+      <family val="1"/>
       <charset val="136"/>
       <scheme val="minor"/>
     </font>
@@ -263,7 +263,7 @@
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="新細明體"/>
-      <family val="2"/>
+      <family val="1"/>
       <charset val="136"/>
       <scheme val="minor"/>
     </font>
@@ -271,13 +271,21 @@
       <sz val="10"/>
       <color rgb="FFFF0000"/>
       <name val="新細明體"/>
-      <family val="2"/>
+      <family val="1"/>
       <charset val="136"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF008000"/>
+      <name val="新細明體"/>
+      <family val="1"/>
+      <charset val="136"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
       <name val="新細明體"/>
       <family val="2"/>
       <charset val="136"/>
@@ -818,7 +826,7 @@
     <xf numFmtId="0" fontId="18" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="33" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -827,7 +835,7 @@
     <xf numFmtId="0" fontId="20" fillId="33" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="17" fontId="19" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -845,22 +853,22 @@
     <xf numFmtId="0" fontId="23" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1218,21 +1226,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Q93"/>
+  <dimension ref="A1:Q55"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.625" customWidth="1"/>
-    <col min="2" max="7" width="9.25" customWidth="1"/>
-    <col min="8" max="8" width="12.125" customWidth="1"/>
-    <col min="9" max="9" width="12.5" customWidth="1"/>
-    <col min="10" max="10" width="9.25" customWidth="1"/>
-    <col min="11" max="11" width="9.75" customWidth="1"/>
-    <col min="12" max="12" width="9.25" customWidth="1"/>
-    <col min="13" max="13" width="12.125" customWidth="1"/>
-    <col min="14" max="14" width="12.5" customWidth="1"/>
-    <col min="15" max="15" width="9.25" customWidth="1"/>
-    <col min="16" max="16" width="9.75" customWidth="1"/>
-    <col min="17" max="17" width="10.625" customWidth="1"/>
+    <col min="1" max="1" width="16.5" customWidth="1"/>
+    <col min="2" max="7" width="13.125" customWidth="1"/>
+    <col min="8" max="8" width="17.125" customWidth="1"/>
+    <col min="9" max="9" width="17.75" customWidth="1"/>
+    <col min="10" max="10" width="13.125" customWidth="1"/>
+    <col min="11" max="11" width="13.75" customWidth="1"/>
+    <col min="12" max="12" width="13.125" customWidth="1"/>
+    <col min="13" max="13" width="17.125" customWidth="1"/>
+    <col min="14" max="14" width="17.75" customWidth="1"/>
+    <col min="15" max="15" width="13.125" customWidth="1"/>
+    <col min="16" max="16" width="13.75" customWidth="1"/>
+    <col min="17" max="17" width="14.375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:17" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
@@ -4084,2020 +4092,6 @@
       </c>
       <c r="Q55" s="10">
         <v>-2.5299999999999998</v>
-      </c>
-    </row>
-    <row r="56" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
-      <c r="A56" s="6">
-        <v>42979</v>
-      </c>
-      <c r="B56" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="C56" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="D56" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="E56" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="F56" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="G56" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="H56" s="8">
-        <v>3.5</v>
-      </c>
-      <c r="I56" s="10">
-        <v>-24.1</v>
-      </c>
-      <c r="J56" s="10">
-        <v>-22.7</v>
-      </c>
-      <c r="K56" s="8">
-        <v>42.92</v>
-      </c>
-      <c r="L56" s="10">
-        <v>-0.49</v>
-      </c>
-      <c r="M56" s="8">
-        <v>3.5</v>
-      </c>
-      <c r="N56" s="10">
-        <v>-24.1</v>
-      </c>
-      <c r="O56" s="10">
-        <v>-22.7</v>
-      </c>
-      <c r="P56" s="8">
-        <v>42.92</v>
-      </c>
-      <c r="Q56" s="10">
-        <v>-0.49</v>
-      </c>
-    </row>
-    <row r="57" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
-      <c r="A57" s="6">
-        <v>42948</v>
-      </c>
-      <c r="B57" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="C57" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="D57" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="E57" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="F57" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="G57" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="H57" s="8">
-        <v>4.6100000000000003</v>
-      </c>
-      <c r="I57" s="9">
-        <v>1.06</v>
-      </c>
-      <c r="J57" s="10">
-        <v>-6.07</v>
-      </c>
-      <c r="K57" s="8">
-        <v>39.42</v>
-      </c>
-      <c r="L57" s="9">
-        <v>1.66</v>
-      </c>
-      <c r="M57" s="8">
-        <v>4.6100000000000003</v>
-      </c>
-      <c r="N57" s="9">
-        <v>1.06</v>
-      </c>
-      <c r="O57" s="10">
-        <v>-6.07</v>
-      </c>
-      <c r="P57" s="8">
-        <v>39.42</v>
-      </c>
-      <c r="Q57" s="9">
-        <v>1.66</v>
-      </c>
-    </row>
-    <row r="58" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
-      <c r="A58" s="6">
-        <v>42917</v>
-      </c>
-      <c r="B58" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="C58" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="D58" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="E58" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="F58" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="G58" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="H58" s="8">
-        <v>4.5599999999999996</v>
-      </c>
-      <c r="I58" s="10">
-        <v>-17.5</v>
-      </c>
-      <c r="J58" s="9">
-        <v>6.31</v>
-      </c>
-      <c r="K58" s="8">
-        <v>34.83</v>
-      </c>
-      <c r="L58" s="9">
-        <v>2.77</v>
-      </c>
-      <c r="M58" s="8">
-        <v>4.5599999999999996</v>
-      </c>
-      <c r="N58" s="10">
-        <v>-17.5</v>
-      </c>
-      <c r="O58" s="9">
-        <v>6.31</v>
-      </c>
-      <c r="P58" s="8">
-        <v>34.83</v>
-      </c>
-      <c r="Q58" s="9">
-        <v>2.77</v>
-      </c>
-    </row>
-    <row r="59" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
-      <c r="A59" s="6">
-        <v>42887</v>
-      </c>
-      <c r="B59" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="C59" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="D59" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="E59" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="F59" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="G59" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="H59" s="8">
-        <v>5.53</v>
-      </c>
-      <c r="I59" s="9">
-        <v>16.600000000000001</v>
-      </c>
-      <c r="J59" s="9">
-        <v>8.31</v>
-      </c>
-      <c r="K59" s="8">
-        <v>30.27</v>
-      </c>
-      <c r="L59" s="9">
-        <v>2.2599999999999998</v>
-      </c>
-      <c r="M59" s="8">
-        <v>5.53</v>
-      </c>
-      <c r="N59" s="9">
-        <v>16.600000000000001</v>
-      </c>
-      <c r="O59" s="9">
-        <v>8.31</v>
-      </c>
-      <c r="P59" s="8">
-        <v>30.27</v>
-      </c>
-      <c r="Q59" s="9">
-        <v>2.2599999999999998</v>
-      </c>
-    </row>
-    <row r="60" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
-      <c r="A60" s="6">
-        <v>42856</v>
-      </c>
-      <c r="B60" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="C60" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="D60" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="E60" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="F60" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="G60" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="H60" s="8">
-        <v>4.74</v>
-      </c>
-      <c r="I60" s="10">
-        <v>-8.9700000000000006</v>
-      </c>
-      <c r="J60" s="10">
-        <v>-5.14</v>
-      </c>
-      <c r="K60" s="8">
-        <v>24.64</v>
-      </c>
-      <c r="L60" s="9">
-        <v>0.27</v>
-      </c>
-      <c r="M60" s="8">
-        <v>4.74</v>
-      </c>
-      <c r="N60" s="10">
-        <v>-8.9700000000000006</v>
-      </c>
-      <c r="O60" s="10">
-        <v>-5.14</v>
-      </c>
-      <c r="P60" s="8">
-        <v>24.64</v>
-      </c>
-      <c r="Q60" s="9">
-        <v>0.27</v>
-      </c>
-    </row>
-    <row r="61" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
-      <c r="A61" s="6">
-        <v>42826</v>
-      </c>
-      <c r="B61" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="C61" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="D61" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="E61" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="F61" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="G61" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="H61" s="8">
-        <v>5.21</v>
-      </c>
-      <c r="I61" s="10">
-        <v>-2.92</v>
-      </c>
-      <c r="J61" s="9">
-        <v>20.3</v>
-      </c>
-      <c r="K61" s="8">
-        <v>19.899999999999999</v>
-      </c>
-      <c r="L61" s="9">
-        <v>1.65</v>
-      </c>
-      <c r="M61" s="8">
-        <v>5.21</v>
-      </c>
-      <c r="N61" s="10">
-        <v>-2.92</v>
-      </c>
-      <c r="O61" s="9">
-        <v>20.3</v>
-      </c>
-      <c r="P61" s="8">
-        <v>19.899999999999999</v>
-      </c>
-      <c r="Q61" s="9">
-        <v>1.65</v>
-      </c>
-    </row>
-    <row r="62" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
-      <c r="A62" s="6">
-        <v>42795</v>
-      </c>
-      <c r="B62" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="C62" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="D62" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="E62" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="F62" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="G62" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="H62" s="8">
-        <v>5.37</v>
-      </c>
-      <c r="I62" s="9">
-        <v>22.8</v>
-      </c>
-      <c r="J62" s="10">
-        <v>-11.7</v>
-      </c>
-      <c r="K62" s="8">
-        <v>14.69</v>
-      </c>
-      <c r="L62" s="10">
-        <v>-3.65</v>
-      </c>
-      <c r="M62" s="8">
-        <v>5.37</v>
-      </c>
-      <c r="N62" s="9">
-        <v>22.8</v>
-      </c>
-      <c r="O62" s="10">
-        <v>-11.7</v>
-      </c>
-      <c r="P62" s="8">
-        <v>14.69</v>
-      </c>
-      <c r="Q62" s="10">
-        <v>-3.65</v>
-      </c>
-    </row>
-    <row r="63" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
-      <c r="A63" s="6">
-        <v>42767</v>
-      </c>
-      <c r="B63" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="C63" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="D63" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="E63" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="F63" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="G63" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="H63" s="8">
-        <v>4.37</v>
-      </c>
-      <c r="I63" s="10">
-        <v>-13.2</v>
-      </c>
-      <c r="J63" s="9">
-        <v>2.41</v>
-      </c>
-      <c r="K63" s="8">
-        <v>9.4</v>
-      </c>
-      <c r="L63" s="9">
-        <v>3.73</v>
-      </c>
-      <c r="M63" s="8">
-        <v>4.37</v>
-      </c>
-      <c r="N63" s="10">
-        <v>-13.2</v>
-      </c>
-      <c r="O63" s="9">
-        <v>2.41</v>
-      </c>
-      <c r="P63" s="8">
-        <v>9.4</v>
-      </c>
-      <c r="Q63" s="9">
-        <v>3.73</v>
-      </c>
-    </row>
-    <row r="64" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
-      <c r="A64" s="6">
-        <v>42736</v>
-      </c>
-      <c r="B64" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="C64" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="D64" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="E64" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="F64" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="G64" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="H64" s="8">
-        <v>5.03</v>
-      </c>
-      <c r="I64" s="9">
-        <v>44.2</v>
-      </c>
-      <c r="J64" s="9">
-        <v>4.91</v>
-      </c>
-      <c r="K64" s="8">
-        <v>5.03</v>
-      </c>
-      <c r="L64" s="9">
-        <v>4.91</v>
-      </c>
-      <c r="M64" s="8">
-        <v>5.03</v>
-      </c>
-      <c r="N64" s="9">
-        <v>44.2</v>
-      </c>
-      <c r="O64" s="9">
-        <v>4.91</v>
-      </c>
-      <c r="P64" s="8">
-        <v>5.03</v>
-      </c>
-      <c r="Q64" s="9">
-        <v>4.91</v>
-      </c>
-    </row>
-    <row r="65" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
-      <c r="A65" s="6">
-        <v>42705</v>
-      </c>
-      <c r="B65" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="C65" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="D65" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="E65" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="F65" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="G65" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="H65" s="8">
-        <v>3.49</v>
-      </c>
-      <c r="I65" s="10">
-        <v>-14.5</v>
-      </c>
-      <c r="J65" s="10">
-        <v>-16.100000000000001</v>
-      </c>
-      <c r="K65" s="8">
-        <v>55.27</v>
-      </c>
-      <c r="L65" s="9">
-        <v>6.57</v>
-      </c>
-      <c r="M65" s="8">
-        <v>3.49</v>
-      </c>
-      <c r="N65" s="10">
-        <v>-14.5</v>
-      </c>
-      <c r="O65" s="10">
-        <v>-16.100000000000001</v>
-      </c>
-      <c r="P65" s="8">
-        <v>55.27</v>
-      </c>
-      <c r="Q65" s="9">
-        <v>6.57</v>
-      </c>
-    </row>
-    <row r="66" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
-      <c r="A66" s="6">
-        <v>42675</v>
-      </c>
-      <c r="B66" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="C66" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="D66" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="E66" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="F66" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="G66" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="H66" s="8">
-        <v>4.08</v>
-      </c>
-      <c r="I66" s="10">
-        <v>-2.11</v>
-      </c>
-      <c r="J66" s="9">
-        <v>6.74</v>
-      </c>
-      <c r="K66" s="8">
-        <v>51.39</v>
-      </c>
-      <c r="L66" s="9">
-        <v>8.7100000000000009</v>
-      </c>
-      <c r="M66" s="8">
-        <v>4.08</v>
-      </c>
-      <c r="N66" s="10">
-        <v>-2.11</v>
-      </c>
-      <c r="O66" s="9">
-        <v>6.74</v>
-      </c>
-      <c r="P66" s="8">
-        <v>51.39</v>
-      </c>
-      <c r="Q66" s="9">
-        <v>8.7100000000000009</v>
-      </c>
-    </row>
-    <row r="67" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
-      <c r="A67" s="6">
-        <v>42644</v>
-      </c>
-      <c r="B67" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="C67" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="D67" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="E67" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="F67" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="G67" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="H67" s="8">
-        <v>4.17</v>
-      </c>
-      <c r="I67" s="10">
-        <v>-7.89</v>
-      </c>
-      <c r="J67" s="9">
-        <v>0.14000000000000001</v>
-      </c>
-      <c r="K67" s="8">
-        <v>47.31</v>
-      </c>
-      <c r="L67" s="9">
-        <v>8.8800000000000008</v>
-      </c>
-      <c r="M67" s="8">
-        <v>4.17</v>
-      </c>
-      <c r="N67" s="10">
-        <v>-7.89</v>
-      </c>
-      <c r="O67" s="9">
-        <v>0.14000000000000001</v>
-      </c>
-      <c r="P67" s="8">
-        <v>47.31</v>
-      </c>
-      <c r="Q67" s="9">
-        <v>8.8800000000000008</v>
-      </c>
-    </row>
-    <row r="68" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
-      <c r="A68" s="6">
-        <v>42614</v>
-      </c>
-      <c r="B68" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="C68" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="D68" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="E68" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="F68" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="G68" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="H68" s="8">
-        <v>4.53</v>
-      </c>
-      <c r="I68" s="10">
-        <v>-7.74</v>
-      </c>
-      <c r="J68" s="9">
-        <v>5.52</v>
-      </c>
-      <c r="K68" s="8">
-        <v>43.13</v>
-      </c>
-      <c r="L68" s="9">
-        <v>9.81</v>
-      </c>
-      <c r="M68" s="8">
-        <v>4.53</v>
-      </c>
-      <c r="N68" s="10">
-        <v>-7.74</v>
-      </c>
-      <c r="O68" s="9">
-        <v>5.52</v>
-      </c>
-      <c r="P68" s="8">
-        <v>43.13</v>
-      </c>
-      <c r="Q68" s="9">
-        <v>9.81</v>
-      </c>
-    </row>
-    <row r="69" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
-      <c r="A69" s="6">
-        <v>42583</v>
-      </c>
-      <c r="B69" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="C69" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="D69" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="E69" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="F69" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="G69" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="H69" s="8">
-        <v>4.91</v>
-      </c>
-      <c r="I69" s="9">
-        <v>14.4</v>
-      </c>
-      <c r="J69" s="9">
-        <v>10.199999999999999</v>
-      </c>
-      <c r="K69" s="8">
-        <v>38.78</v>
-      </c>
-      <c r="L69" s="9">
-        <v>10.8</v>
-      </c>
-      <c r="M69" s="8">
-        <v>4.91</v>
-      </c>
-      <c r="N69" s="9">
-        <v>14.4</v>
-      </c>
-      <c r="O69" s="9">
-        <v>10.199999999999999</v>
-      </c>
-      <c r="P69" s="8">
-        <v>38.78</v>
-      </c>
-      <c r="Q69" s="9">
-        <v>10.8</v>
-      </c>
-    </row>
-    <row r="70" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
-      <c r="A70" s="6">
-        <v>42552</v>
-      </c>
-      <c r="B70" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="C70" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="D70" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="E70" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="F70" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="G70" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="H70" s="8">
-        <v>4.29</v>
-      </c>
-      <c r="I70" s="10">
-        <v>-15.9</v>
-      </c>
-      <c r="J70" s="10">
-        <v>-8.5</v>
-      </c>
-      <c r="K70" s="8">
-        <v>33.89</v>
-      </c>
-      <c r="L70" s="9">
-        <v>11</v>
-      </c>
-      <c r="M70" s="8">
-        <v>4.29</v>
-      </c>
-      <c r="N70" s="10">
-        <v>-15.9</v>
-      </c>
-      <c r="O70" s="10">
-        <v>-8.5</v>
-      </c>
-      <c r="P70" s="8">
-        <v>33.89</v>
-      </c>
-      <c r="Q70" s="9">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="71" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
-      <c r="A71" s="6">
-        <v>42522</v>
-      </c>
-      <c r="B71" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="C71" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="D71" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="E71" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="F71" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="G71" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="H71" s="8">
-        <v>5.1100000000000003</v>
-      </c>
-      <c r="I71" s="9">
-        <v>2.14</v>
-      </c>
-      <c r="J71" s="9">
-        <v>26.1</v>
-      </c>
-      <c r="K71" s="8">
-        <v>29.6</v>
-      </c>
-      <c r="L71" s="9">
-        <v>14.5</v>
-      </c>
-      <c r="M71" s="8">
-        <v>5.1100000000000003</v>
-      </c>
-      <c r="N71" s="9">
-        <v>2.14</v>
-      </c>
-      <c r="O71" s="9">
-        <v>26.1</v>
-      </c>
-      <c r="P71" s="8">
-        <v>29.6</v>
-      </c>
-      <c r="Q71" s="9">
-        <v>14.5</v>
-      </c>
-    </row>
-    <row r="72" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
-      <c r="A72" s="6">
-        <v>42491</v>
-      </c>
-      <c r="B72" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="C72" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="D72" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="E72" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="F72" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="G72" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="H72" s="8">
-        <v>5</v>
-      </c>
-      <c r="I72" s="9">
-        <v>15.4</v>
-      </c>
-      <c r="J72" s="9">
-        <v>14.6</v>
-      </c>
-      <c r="K72" s="8">
-        <v>24.57</v>
-      </c>
-      <c r="L72" s="9">
-        <v>12.7</v>
-      </c>
-      <c r="M72" s="8">
-        <v>5</v>
-      </c>
-      <c r="N72" s="9">
-        <v>15.4</v>
-      </c>
-      <c r="O72" s="9">
-        <v>14.6</v>
-      </c>
-      <c r="P72" s="8">
-        <v>24.57</v>
-      </c>
-      <c r="Q72" s="9">
-        <v>12.7</v>
-      </c>
-    </row>
-    <row r="73" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
-      <c r="A73" s="6">
-        <v>42461</v>
-      </c>
-      <c r="B73" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="C73" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="D73" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="E73" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="F73" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="G73" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="H73" s="8">
-        <v>4.33</v>
-      </c>
-      <c r="I73" s="10">
-        <v>-28.8</v>
-      </c>
-      <c r="J73" s="9">
-        <v>1.31</v>
-      </c>
-      <c r="K73" s="8">
-        <v>19.57</v>
-      </c>
-      <c r="L73" s="9">
-        <v>12.3</v>
-      </c>
-      <c r="M73" s="8">
-        <v>4.33</v>
-      </c>
-      <c r="N73" s="10">
-        <v>-28.8</v>
-      </c>
-      <c r="O73" s="9">
-        <v>1.31</v>
-      </c>
-      <c r="P73" s="8">
-        <v>19.57</v>
-      </c>
-      <c r="Q73" s="9">
-        <v>12.3</v>
-      </c>
-    </row>
-    <row r="74" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
-      <c r="A74" s="6">
-        <v>42430</v>
-      </c>
-      <c r="B74" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="C74" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="D74" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="E74" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="F74" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="G74" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="H74" s="8">
-        <v>6.08</v>
-      </c>
-      <c r="I74" s="9">
-        <v>42.4</v>
-      </c>
-      <c r="J74" s="9">
-        <v>25.2</v>
-      </c>
-      <c r="K74" s="8">
-        <v>15.24</v>
-      </c>
-      <c r="L74" s="9">
-        <v>15.8</v>
-      </c>
-      <c r="M74" s="8">
-        <v>6.08</v>
-      </c>
-      <c r="N74" s="9">
-        <v>42.4</v>
-      </c>
-      <c r="O74" s="9">
-        <v>25.2</v>
-      </c>
-      <c r="P74" s="8">
-        <v>15.24</v>
-      </c>
-      <c r="Q74" s="9">
-        <v>15.8</v>
-      </c>
-    </row>
-    <row r="75" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
-      <c r="A75" s="6">
-        <v>42401</v>
-      </c>
-      <c r="B75" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="C75" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="D75" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="E75" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="F75" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="G75" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="H75" s="8">
-        <v>4.2699999999999996</v>
-      </c>
-      <c r="I75" s="10">
-        <v>-11.1</v>
-      </c>
-      <c r="J75" s="9">
-        <v>18.3</v>
-      </c>
-      <c r="K75" s="8">
-        <v>9.07</v>
-      </c>
-      <c r="L75" s="9">
-        <v>9.1199999999999992</v>
-      </c>
-      <c r="M75" s="8">
-        <v>4.2699999999999996</v>
-      </c>
-      <c r="N75" s="10">
-        <v>-11.1</v>
-      </c>
-      <c r="O75" s="9">
-        <v>18.3</v>
-      </c>
-      <c r="P75" s="8">
-        <v>9.07</v>
-      </c>
-      <c r="Q75" s="9">
-        <v>9.1199999999999992</v>
-      </c>
-    </row>
-    <row r="76" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
-      <c r="A76" s="6">
-        <v>42370</v>
-      </c>
-      <c r="B76" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="C76" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="D76" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="E76" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="F76" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="G76" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="H76" s="8">
-        <v>4.8</v>
-      </c>
-      <c r="I76" s="9">
-        <v>15.3</v>
-      </c>
-      <c r="J76" s="9">
-        <v>2.06</v>
-      </c>
-      <c r="K76" s="8">
-        <v>4.8</v>
-      </c>
-      <c r="L76" s="9">
-        <v>2.06</v>
-      </c>
-      <c r="M76" s="8">
-        <v>4.8</v>
-      </c>
-      <c r="N76" s="9">
-        <v>15.3</v>
-      </c>
-      <c r="O76" s="9">
-        <v>2.06</v>
-      </c>
-      <c r="P76" s="8">
-        <v>4.8</v>
-      </c>
-      <c r="Q76" s="9">
-        <v>2.06</v>
-      </c>
-    </row>
-    <row r="77" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
-      <c r="A77" s="6">
-        <v>42339</v>
-      </c>
-      <c r="B77" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="C77" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="D77" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="E77" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="F77" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="G77" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="H77" s="8">
-        <v>4.16</v>
-      </c>
-      <c r="I77" s="9">
-        <v>8.81</v>
-      </c>
-      <c r="J77" s="9">
-        <v>6.19</v>
-      </c>
-      <c r="K77" s="8">
-        <v>51.86</v>
-      </c>
-      <c r="L77" s="9">
-        <v>8.07</v>
-      </c>
-      <c r="M77" s="8">
-        <v>4.16</v>
-      </c>
-      <c r="N77" s="9">
-        <v>8.81</v>
-      </c>
-      <c r="O77" s="9">
-        <v>6.19</v>
-      </c>
-      <c r="P77" s="8">
-        <v>51.86</v>
-      </c>
-      <c r="Q77" s="9">
-        <v>8.07</v>
-      </c>
-    </row>
-    <row r="78" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
-      <c r="A78" s="6">
-        <v>42309</v>
-      </c>
-      <c r="B78" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="C78" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="D78" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="E78" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="F78" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="G78" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="H78" s="8">
-        <v>3.82</v>
-      </c>
-      <c r="I78" s="10">
-        <v>-8.17</v>
-      </c>
-      <c r="J78" s="9">
-        <v>15.7</v>
-      </c>
-      <c r="K78" s="8">
-        <v>47.27</v>
-      </c>
-      <c r="L78" s="9">
-        <v>7.27</v>
-      </c>
-      <c r="M78" s="8">
-        <v>3.82</v>
-      </c>
-      <c r="N78" s="10">
-        <v>-8.17</v>
-      </c>
-      <c r="O78" s="9">
-        <v>15.7</v>
-      </c>
-      <c r="P78" s="8">
-        <v>47.27</v>
-      </c>
-      <c r="Q78" s="9">
-        <v>7.27</v>
-      </c>
-    </row>
-    <row r="79" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
-      <c r="A79" s="6">
-        <v>42278</v>
-      </c>
-      <c r="B79" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="C79" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="D79" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="E79" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="F79" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="G79" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="H79" s="8">
-        <v>4.17</v>
-      </c>
-      <c r="I79" s="10">
-        <v>-3.78</v>
-      </c>
-      <c r="J79" s="9">
-        <v>12</v>
-      </c>
-      <c r="K79" s="8">
-        <v>43.45</v>
-      </c>
-      <c r="L79" s="9">
-        <v>6.58</v>
-      </c>
-      <c r="M79" s="8">
-        <v>4.17</v>
-      </c>
-      <c r="N79" s="10">
-        <v>-3.78</v>
-      </c>
-      <c r="O79" s="9">
-        <v>12</v>
-      </c>
-      <c r="P79" s="8">
-        <v>43.45</v>
-      </c>
-      <c r="Q79" s="9">
-        <v>6.58</v>
-      </c>
-    </row>
-    <row r="80" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
-      <c r="A80" s="6">
-        <v>42248</v>
-      </c>
-      <c r="B80" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="C80" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="D80" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="E80" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="F80" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="G80" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="H80" s="8">
-        <v>4.29</v>
-      </c>
-      <c r="I80" s="10">
-        <v>-3.64</v>
-      </c>
-      <c r="J80" s="9">
-        <v>29.4</v>
-      </c>
-      <c r="K80" s="8">
-        <v>39.28</v>
-      </c>
-      <c r="L80" s="9">
-        <v>6.04</v>
-      </c>
-      <c r="M80" s="8">
-        <v>4.29</v>
-      </c>
-      <c r="N80" s="10">
-        <v>-3.64</v>
-      </c>
-      <c r="O80" s="9">
-        <v>29.4</v>
-      </c>
-      <c r="P80" s="8">
-        <v>39.28</v>
-      </c>
-      <c r="Q80" s="9">
-        <v>6.04</v>
-      </c>
-    </row>
-    <row r="81" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
-      <c r="A81" s="6">
-        <v>42217</v>
-      </c>
-      <c r="B81" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="C81" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="D81" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="E81" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="F81" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="G81" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="H81" s="8">
-        <v>4.45</v>
-      </c>
-      <c r="I81" s="10">
-        <v>-5.03</v>
-      </c>
-      <c r="J81" s="9">
-        <v>13.1</v>
-      </c>
-      <c r="K81" s="8">
-        <v>34.99</v>
-      </c>
-      <c r="L81" s="9">
-        <v>3.74</v>
-      </c>
-      <c r="M81" s="8">
-        <v>4.45</v>
-      </c>
-      <c r="N81" s="10">
-        <v>-5.03</v>
-      </c>
-      <c r="O81" s="9">
-        <v>13.1</v>
-      </c>
-      <c r="P81" s="8">
-        <v>34.99</v>
-      </c>
-      <c r="Q81" s="9">
-        <v>3.74</v>
-      </c>
-    </row>
-    <row r="82" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
-      <c r="A82" s="6">
-        <v>42186</v>
-      </c>
-      <c r="B82" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="C82" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="D82" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="E82" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="F82" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="G82" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="H82" s="8">
-        <v>4.6900000000000004</v>
-      </c>
-      <c r="I82" s="9">
-        <v>12.4</v>
-      </c>
-      <c r="J82" s="9">
-        <v>14.6</v>
-      </c>
-      <c r="K82" s="8">
-        <v>30.54</v>
-      </c>
-      <c r="L82" s="9">
-        <v>2.4300000000000002</v>
-      </c>
-      <c r="M82" s="8">
-        <v>4.6900000000000004</v>
-      </c>
-      <c r="N82" s="9">
-        <v>12.4</v>
-      </c>
-      <c r="O82" s="9">
-        <v>14.6</v>
-      </c>
-      <c r="P82" s="8">
-        <v>30.54</v>
-      </c>
-      <c r="Q82" s="9">
-        <v>2.4300000000000002</v>
-      </c>
-    </row>
-    <row r="83" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
-      <c r="A83" s="6">
-        <v>42156</v>
-      </c>
-      <c r="B83" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="C83" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="D83" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="E83" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="F83" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="G83" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="H83" s="8">
-        <v>4.05</v>
-      </c>
-      <c r="I83" s="10">
-        <v>-7.14</v>
-      </c>
-      <c r="J83" s="10">
-        <v>-9.93</v>
-      </c>
-      <c r="K83" s="8">
-        <v>25.85</v>
-      </c>
-      <c r="L83" s="9">
-        <v>0.5</v>
-      </c>
-      <c r="M83" s="8">
-        <v>4.05</v>
-      </c>
-      <c r="N83" s="10">
-        <v>-7.14</v>
-      </c>
-      <c r="O83" s="10">
-        <v>-9.93</v>
-      </c>
-      <c r="P83" s="8">
-        <v>25.85</v>
-      </c>
-      <c r="Q83" s="9">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="84" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
-      <c r="A84" s="6">
-        <v>42125</v>
-      </c>
-      <c r="B84" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="C84" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="D84" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="E84" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="F84" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="G84" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="H84" s="8">
-        <v>4.3600000000000003</v>
-      </c>
-      <c r="I84" s="9">
-        <v>2.02</v>
-      </c>
-      <c r="J84" s="10">
-        <v>-6.65</v>
-      </c>
-      <c r="K84" s="8">
-        <v>21.8</v>
-      </c>
-      <c r="L84" s="9">
-        <v>2.71</v>
-      </c>
-      <c r="M84" s="8">
-        <v>4.3600000000000003</v>
-      </c>
-      <c r="N84" s="9">
-        <v>2.02</v>
-      </c>
-      <c r="O84" s="10">
-        <v>-6.65</v>
-      </c>
-      <c r="P84" s="8">
-        <v>21.8</v>
-      </c>
-      <c r="Q84" s="9">
-        <v>2.71</v>
-      </c>
-    </row>
-    <row r="85" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
-      <c r="A85" s="6">
-        <v>42095</v>
-      </c>
-      <c r="B85" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="C85" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="D85" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="E85" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="F85" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="G85" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="H85" s="8">
-        <v>4.2699999999999996</v>
-      </c>
-      <c r="I85" s="10">
-        <v>-9.4499999999999993</v>
-      </c>
-      <c r="J85" s="10">
-        <v>-0.5</v>
-      </c>
-      <c r="K85" s="8">
-        <v>17.440000000000001</v>
-      </c>
-      <c r="L85" s="9">
-        <v>5.35</v>
-      </c>
-      <c r="M85" s="8">
-        <v>4.2699999999999996</v>
-      </c>
-      <c r="N85" s="10">
-        <v>-9.4499999999999993</v>
-      </c>
-      <c r="O85" s="10">
-        <v>-0.5</v>
-      </c>
-      <c r="P85" s="8">
-        <v>17.440000000000001</v>
-      </c>
-      <c r="Q85" s="9">
-        <v>5.35</v>
-      </c>
-    </row>
-    <row r="86" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
-      <c r="A86" s="6">
-        <v>42064</v>
-      </c>
-      <c r="B86" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="C86" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="D86" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="E86" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="F86" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="G86" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="H86" s="8">
-        <v>4.8600000000000003</v>
-      </c>
-      <c r="I86" s="9">
-        <v>34.700000000000003</v>
-      </c>
-      <c r="J86" s="9">
-        <v>0.98</v>
-      </c>
-      <c r="K86" s="8">
-        <v>13.16</v>
-      </c>
-      <c r="L86" s="9">
-        <v>7.4</v>
-      </c>
-      <c r="M86" s="8">
-        <v>4.8600000000000003</v>
-      </c>
-      <c r="N86" s="9">
-        <v>34.700000000000003</v>
-      </c>
-      <c r="O86" s="9">
-        <v>0.98</v>
-      </c>
-      <c r="P86" s="8">
-        <v>13.16</v>
-      </c>
-      <c r="Q86" s="9">
-        <v>7.4</v>
-      </c>
-    </row>
-    <row r="87" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
-      <c r="A87" s="6">
-        <v>42036</v>
-      </c>
-      <c r="B87" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="C87" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="D87" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="E87" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="F87" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="G87" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="H87" s="8">
-        <v>3.61</v>
-      </c>
-      <c r="I87" s="10">
-        <v>-23.3</v>
-      </c>
-      <c r="J87" s="9">
-        <v>5.77</v>
-      </c>
-      <c r="K87" s="8">
-        <v>8.31</v>
-      </c>
-      <c r="L87" s="9">
-        <v>11.5</v>
-      </c>
-      <c r="M87" s="8">
-        <v>3.61</v>
-      </c>
-      <c r="N87" s="10">
-        <v>-23.3</v>
-      </c>
-      <c r="O87" s="9">
-        <v>5.77</v>
-      </c>
-      <c r="P87" s="8">
-        <v>8.31</v>
-      </c>
-      <c r="Q87" s="9">
-        <v>11.5</v>
-      </c>
-    </row>
-    <row r="88" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
-      <c r="A88" s="6">
-        <v>42005</v>
-      </c>
-      <c r="B88" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="C88" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="D88" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="E88" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="F88" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="G88" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="H88" s="8">
-        <v>4.7</v>
-      </c>
-      <c r="I88" s="9">
-        <v>29.1</v>
-      </c>
-      <c r="J88" s="9">
-        <v>16.399999999999999</v>
-      </c>
-      <c r="K88" s="8">
-        <v>4.7</v>
-      </c>
-      <c r="L88" s="9">
-        <v>16.399999999999999</v>
-      </c>
-      <c r="M88" s="8">
-        <v>4.7</v>
-      </c>
-      <c r="N88" s="9">
-        <v>29.1</v>
-      </c>
-      <c r="O88" s="9">
-        <v>16.399999999999999</v>
-      </c>
-      <c r="P88" s="8">
-        <v>4.7</v>
-      </c>
-      <c r="Q88" s="9">
-        <v>16.399999999999999</v>
-      </c>
-    </row>
-    <row r="89" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
-      <c r="A89" s="6">
-        <v>41974</v>
-      </c>
-      <c r="B89" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="C89" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="D89" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="E89" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="F89" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="G89" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="H89" s="8">
-        <v>3.92</v>
-      </c>
-      <c r="I89" s="9">
-        <v>18.600000000000001</v>
-      </c>
-      <c r="J89" s="10">
-        <v>-8.0299999999999994</v>
-      </c>
-      <c r="K89" s="8">
-        <v>47.99</v>
-      </c>
-      <c r="L89" s="9">
-        <v>11.4</v>
-      </c>
-      <c r="M89" s="8">
-        <v>3.92</v>
-      </c>
-      <c r="N89" s="9">
-        <v>18.600000000000001</v>
-      </c>
-      <c r="O89" s="10">
-        <v>-8.0299999999999994</v>
-      </c>
-      <c r="P89" s="8">
-        <v>47.99</v>
-      </c>
-      <c r="Q89" s="9">
-        <v>11.4</v>
-      </c>
-    </row>
-    <row r="90" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
-      <c r="A90" s="6">
-        <v>41944</v>
-      </c>
-      <c r="B90" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="C90" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="D90" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="E90" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="F90" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="G90" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="H90" s="8">
-        <v>3.3</v>
-      </c>
-      <c r="I90" s="10">
-        <v>-11.1</v>
-      </c>
-      <c r="J90" s="9">
-        <v>4.92</v>
-      </c>
-      <c r="K90" s="8">
-        <v>44.07</v>
-      </c>
-      <c r="L90" s="9">
-        <v>13.5</v>
-      </c>
-      <c r="M90" s="8">
-        <v>3.3</v>
-      </c>
-      <c r="N90" s="10">
-        <v>-11.1</v>
-      </c>
-      <c r="O90" s="9">
-        <v>4.92</v>
-      </c>
-      <c r="P90" s="8">
-        <v>44.07</v>
-      </c>
-      <c r="Q90" s="9">
-        <v>13.5</v>
-      </c>
-    </row>
-    <row r="91" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
-      <c r="A91" s="6">
-        <v>41913</v>
-      </c>
-      <c r="B91" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="C91" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="D91" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="E91" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="F91" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="G91" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="H91" s="8">
-        <v>3.72</v>
-      </c>
-      <c r="I91" s="9">
-        <v>12.1</v>
-      </c>
-      <c r="J91" s="9">
-        <v>5.0999999999999996</v>
-      </c>
-      <c r="K91" s="8">
-        <v>40.76</v>
-      </c>
-      <c r="L91" s="9">
-        <v>14.2</v>
-      </c>
-      <c r="M91" s="8">
-        <v>3.72</v>
-      </c>
-      <c r="N91" s="9">
-        <v>12.1</v>
-      </c>
-      <c r="O91" s="9">
-        <v>5.0999999999999996</v>
-      </c>
-      <c r="P91" s="8">
-        <v>40.76</v>
-      </c>
-      <c r="Q91" s="9">
-        <v>14.2</v>
-      </c>
-    </row>
-    <row r="92" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
-      <c r="A92" s="6">
-        <v>41883</v>
-      </c>
-      <c r="B92" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="C92" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="D92" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="E92" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="F92" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="G92" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="H92" s="8">
-        <v>3.32</v>
-      </c>
-      <c r="I92" s="10">
-        <v>-15.3</v>
-      </c>
-      <c r="J92" s="10">
-        <v>-13.5</v>
-      </c>
-      <c r="K92" s="8">
-        <v>37.049999999999997</v>
-      </c>
-      <c r="L92" s="9">
-        <v>14.2</v>
-      </c>
-      <c r="M92" s="8">
-        <v>3.32</v>
-      </c>
-      <c r="N92" s="10">
-        <v>-15.3</v>
-      </c>
-      <c r="O92" s="10">
-        <v>-13.5</v>
-      </c>
-      <c r="P92" s="8">
-        <v>37.049999999999997</v>
-      </c>
-      <c r="Q92" s="9">
-        <v>14.2</v>
-      </c>
-    </row>
-    <row r="93" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
-      <c r="A93" s="6">
-        <v>41852</v>
-      </c>
-      <c r="B93" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="C93" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="D93" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="E93" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="F93" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="G93" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="H93" s="8">
-        <v>3.94</v>
-      </c>
-      <c r="I93" s="10">
-        <v>-3.78</v>
-      </c>
-      <c r="J93" s="9">
-        <v>10.5</v>
-      </c>
-      <c r="K93" s="8">
-        <v>33.729999999999997</v>
-      </c>
-      <c r="L93" s="9">
-        <v>18.7</v>
-      </c>
-      <c r="M93" s="8">
-        <v>3.94</v>
-      </c>
-      <c r="N93" s="10">
-        <v>-3.78</v>
-      </c>
-      <c r="O93" s="9">
-        <v>10.5</v>
-      </c>
-      <c r="P93" s="8">
-        <v>33.729999999999997</v>
-      </c>
-      <c r="Q93" s="9">
-        <v>18.7</v>
       </c>
     </row>
   </sheetData>
@@ -6115,7 +4109,7 @@
     <mergeCell ref="H2:J2"/>
     <mergeCell ref="K2:L2"/>
   </mergeCells>
-  <phoneticPr fontId="24" type="noConversion"/>
+  <phoneticPr fontId="25" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>